--- a/v2/T&C_Code/Inputs/ERW_MOD_PARAM_parameters.xlsx
+++ b/v2/T&C_Code/Inputs/ERW_MOD_PARAM_parameters.xlsx
@@ -50,7 +50,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -124,11 +124,12 @@
       </bottom>
       <diagonal/>
     </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -177,6 +178,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -254,7 +256,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -371,7 +373,7 @@
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill rotWithShape="true">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -395,9 +397,9 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="5400000" scaled="false"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill rotWithShape="true">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -421,7 +423,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="5400000" scaled="false"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -456,7 +458,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="false">
               <a:srgbClr val="000000">
                 <a:alpha val="63000"/>
               </a:srgbClr>
@@ -474,7 +476,7 @@
             <a:satMod val="170000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill rotWithShape="true">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -499,7 +501,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="5400000" scaled="false"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
@@ -1052,7 +1054,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI6"/>
+  <dimension ref="A1:AJ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.1015625" customWidth="1" min="1" max="1"/>
@@ -1069,7 +1071,7 @@
     <col width="23.68359375" customWidth="1" min="12" max="12"/>
     <col width="12.3125" customWidth="1" min="13" max="13"/>
     <col width="11.3125" bestFit="1" customWidth="1" min="14" max="14"/>
-    <col width="12.5234375" customWidth="1" min="15" max="15"/>
+    <col width="4.7109375" customWidth="1" min="15" max="15"/>
     <col width="12.3125" customWidth="1" min="16" max="16"/>
     <col width="11.5234375" customWidth="1" min="17" max="23"/>
     <col width="34.68359375" customWidth="1" min="24" max="24"/>
@@ -1257,6 +1259,11 @@
           <t>pH_DilutionFactor</t>
         </is>
       </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>M_rock_event</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
@@ -1318,7 +1325,7 @@
         </is>
       </c>
       <c r="O2" s="7" t="n">
-        <v>8.6</v>
+        <v>13</v>
       </c>
       <c r="P2" s="7" t="n">
         <v>0</v>
@@ -1358,7 +1365,10 @@
         <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>2</v>
+        <v>2.5</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>5000</v>
       </c>
     </row>
     <row r="3">
@@ -1421,7 +1431,7 @@
         </is>
       </c>
       <c r="O3" s="7" t="n">
-        <v>8.6</v>
+        <v>13</v>
       </c>
       <c r="P3" s="7" t="n">
         <v>0</v>
@@ -1440,17 +1450,16 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>["albite", "ferroactinolite", "epidote", "chlorite","quartz"]</t>
+          <t>["albite", "ferroactinolite", "epidote", "chlorite","quartz","calcite"]</t>
         </is>
       </c>
       <c r="AA3" s="1" t="inlineStr">
         <is>
-          <t>[0.196,0.116,0.256,0.363,0.052]</t>
-        </is>
-      </c>
-      <c r="AB3">
-        <f>3*1000000</f>
-        <v/>
+          <t>[0.196,0.116,0.256,0.363,0.052,0.0054]</t>
+        </is>
+      </c>
+      <c r="AB3" t="n">
+        <v>3000000</v>
       </c>
       <c r="AE3" t="n">
         <v>1.02</v>
@@ -1462,7 +1471,10 @@
         <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>2</v>
+        <v>2.5</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>5000</v>
       </c>
     </row>
     <row r="4">
@@ -1515,7 +1527,7 @@
         </is>
       </c>
       <c r="O4" s="7" t="n">
-        <v>8.6</v>
+        <v>13</v>
       </c>
       <c r="P4" s="7" t="n">
         <v>0</v>
@@ -1537,7 +1549,10 @@
         <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>2</v>
+        <v>2.5</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -1590,7 +1605,7 @@
         </is>
       </c>
       <c r="O5" s="7" t="n">
-        <v>8.6</v>
+        <v>13</v>
       </c>
       <c r="P5" s="7" t="n">
         <v>0</v>
@@ -1612,7 +1627,10 @@
         <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>2</v>
+        <v>2.5</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -1675,7 +1693,7 @@
         </is>
       </c>
       <c r="O6" s="7" t="n">
-        <v>8.6</v>
+        <v>13</v>
       </c>
       <c r="P6" s="7" t="n">
         <v>0</v>
@@ -1715,7 +1733,116 @@
         <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>2</v>
+        <v>2.5</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Urbana (US)</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Kantola</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="n">
+        <v>40.062778</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>-88.196111</v>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>crop_calcite_agronomic</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>Kantola</t>
+        </is>
+      </c>
+      <c r="J7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Kantola</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>blueridge_CDF_data.json</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Blueridge</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>silty loam</t>
+        </is>
+      </c>
+      <c r="O7" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="P7" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" s="7" t="n"/>
+      <c r="S7" s="7" t="n"/>
+      <c r="T7" s="7" t="n"/>
+      <c r="U7" s="7" t="n"/>
+      <c r="V7" s="7" t="n"/>
+      <c r="W7" s="7" t="n"/>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>["calcite"]</t>
+        </is>
+      </c>
+      <c r="AA7" s="1" t="inlineStr">
+        <is>
+          <t>[1]</t>
+        </is>
+      </c>
+      <c r="AB7" t="n">
+        <v>2710000</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>500</v>
       </c>
     </row>
   </sheetData>
